--- a/daily_matches/job_matches_2026-05-09.xlsx
+++ b/daily_matches/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Glue, Dataflow, FastAPI, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Fractional/Part-Time CTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Azure ML, MLflow</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79249e7989055f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=668daa117d5cd90c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fractional CTO- Chicago</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb61f67fa9a3b09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Fractional/Part-Time CTO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Redshift, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, Redshift, Tableau</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=18922cc00f47c2b7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NextGen Federal Systems</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>Data Scientist, Copilot, S3, Glue, Redshift, CI/CD, Git, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402a8cbe67e1b3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, S3, Glue, Athena, Docker, Snowflake, PySpark, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Redshift, MLflow, Docker, Git, Redshift</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,242 +706,242 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0942c31426070e80</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Research Engineer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, PyTorch, YOLO, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Redshift, Docker, Snowflake, Redshift, PySpark, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90027fd020cb014</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5d6d0295586b6a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Java/Cloud/AI/ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, PostgreSQL, Tableau, Power BI</t>
+          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=de820db84e60fd44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Machine Learning Engineer - Healthcare</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunter Douglas</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683eef206a8ca84c</t>
+          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hunter Douglas</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, Keras, Docker, Git, Snowflake, PySpark, Tableau, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3b3c9eb487e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea571945534d0f4a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research InternÂ - GHAI-3</t>
+          <t>Engineer III, SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, XGBoost, LightGBM, Docker, Git, Matplotlib, Seaborn, Python, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb67ed5160ea12</t>
+          <t>https://www.indeed.com/viewjob?jk=6baf774b1b56a4a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>Senior Software Engineer, Emerging Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077b685021f689f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1eea3b935fcd9c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer IV, Site Reliability</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=c62872785b033cfa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Data Scientist Associate - Payments</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, EC2, Kinesis, AKS, Terraform, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=816bd099ab46e879</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intelex</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, R, Java, Scala</t>
+          <t>RAG, Kinesis, CI/CD, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2631ed0a45f45ee</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (WMS)</t>
+          <t>Healthcare Data Analyst or Senior Data Analyst, Analytics Hub</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luminize</t>
+          <t>ECG Management Consultants</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, AKS, Git, Snowflake, BigQuery, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f1657c967fb8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef86042740fa345</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hendrickson</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woodridge, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676c56d27c469638</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6020d304f8274</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=a968c51f077ce01b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=d29c6cb5a640f955</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Azure ML, Databricks, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=068ebfae4530aaee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=e231e1672de64f27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. AI Systems Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d195c174f1b74</t>
+          <t>https://www.indeed.com/viewjob?jk=f26c66c9dcab70b1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science - Analyst 3</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Tableau, Python, SQL, R, A/B Testing</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d415480076106c</t>
+          <t>https://www.indeed.com/viewjob?jk=eccaf065ef4262dd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TEAK</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Terraform, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63855bcc751daa0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd26ebbfb7d1f13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Redshift, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5d907f6163029</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Release Automation Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79d50d9e169954</t>
+          <t>https://www.indeed.com/viewjob?jk=aa795a4386fc054f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior .Net Full Stack Software Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zelis Healthcare</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebfe5a85a780b93</t>
+          <t>https://www.indeed.com/viewjob?jk=9697d9ebfbba3ebe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0577ba5ffdb8308a</t>
+          <t>https://www.indeed.com/viewjob?jk=3acf7e6c406f831f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Professional Software/Data Scientist/Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Geosyntec Consultants, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b40cd5efc1a9cda</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab230c037c30eae</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Product Enablement Specialist</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d0aae32b047b42</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4805e2f0b5d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMTS Quality Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a85859b016beca</t>
+          <t>https://www.indeed.com/viewjob?jk=12ddf94be7b9459a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=af6176f596736374</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=17edad0fcd1ed4d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce6e42b8aa0d150</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=20e7716fba751697</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Cloud Architect - Kubernetes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,637 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Apache Airflow, Terraform, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Clearwater Analytics (CWAN)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9c362111594082</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data Science Intern</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>DZYNE Technologies LLC.</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Fairfax, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>PostgreSQL, MySQL, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a326a34a79f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=eefc6cec4372930d</t>
         </is>
       </c>
     </row>
